--- a/Hoadon/HD2026/HDRa/4/3502412669_Hoadondientu.xlsx
+++ b/Hoadon/HD2026/HDRa/4/3502412669_Hoadondientu.xlsx
@@ -1389,6 +1389,417 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C26TDT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502412669</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI SẢN XUẤT TÂN ĐỨC THỊNH</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>3502570030</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SAO KIM EBM</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>274 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>4037037.0</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>322963.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13" t="n">
+        <v>4360000.0</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C26TDT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502412669</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI SẢN XUẤT TÂN ĐỨC THỊNH</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>3501612295</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG QUỐC THỊNH</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Số 1633/10 Đường Võ Nguyên Giáp, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>1740909.0</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>174091.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13" t="n">
+        <v>1915000.0</v>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C26TDT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502412669</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI SẢN XUẤT TÂN ĐỨC THỊNH</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>3501612295</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG QUỐC THỊNH</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Số 1633/10 Đường Võ Nguyên Giáp, Phường Phước Thắng, TP Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>2722222.0</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>217778.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13" t="n">
+        <v>2940000.0</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C26TDT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502412669</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI SẢN XUẤT TÂN ĐỨC THỊNH</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>3502570030</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH SAO KIM EBM</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>274 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>1481482.0</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>118518.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13" t="n">
+        <v>1600000.0</v>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C26TDT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502412669</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI SẢN XUẤT TÂN ĐỨC THỊNH</t>
+        </is>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Hoàng Thị Vinh</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>229/22A đường 30/4, P. Rạch Dừa, TP. Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>9268519.0</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>741481.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13" t="n">
+        <v>1.001E7</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
